--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487535_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487535_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7876</v>
+        <v>7.2447</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7643</v>
+        <v>3.0877</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0233</v>
+        <v>4.157</v>
       </c>
       <c r="G2" t="n">
         <v>4.6295</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5884</v>
+        <v>1.0456</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3305</v>
+        <v>0.654</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2579</v>
+        <v>0.3916</v>
       </c>
       <c r="V2" t="n">
         <v>3.5281</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>J. GONZALEZ DACAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3928</v>
+        <v>5.7818</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7497</v>
+        <v>3.6809</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6431</v>
+        <v>2.1009</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8158</v>
+        <v>6.0387</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8044</v>
+        <v>2.5785</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0115</v>
+        <v>3.4601</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6119</v>
+        <v>4.9878</v>
       </c>
       <c r="K3" t="n">
-        <v>1.844</v>
+        <v>2.0942</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7679</v>
+        <v>2.8936</v>
       </c>
       <c r="M3" t="n">
-        <v>2.2039</v>
+        <v>1.0509</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9603</v>
+        <v>0.4843</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2436</v>
+        <v>0.5666</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7834</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1543</v>
+        <v>-1.9585</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>2.577</v>
+        <v>0.4102</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2921</v>
+        <v>0.6516</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2849</v>
+        <v>-0.2414</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GONZALEZ DACAL</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7131</v>
+        <v>4.0071</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0934</v>
+        <v>0.8452</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6197</v>
+        <v>3.162</v>
       </c>
       <c r="G4" t="n">
-        <v>6.0387</v>
+        <v>4.8158</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5785</v>
+        <v>2.8044</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4601</v>
+        <v>2.0115</v>
       </c>
       <c r="J4" t="n">
-        <v>4.9878</v>
+        <v>2.6119</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0942</v>
+        <v>1.844</v>
       </c>
       <c r="L4" t="n">
-        <v>2.8936</v>
+        <v>0.7679</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0509</v>
+        <v>2.2039</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4843</v>
+        <v>0.9603</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5666</v>
+        <v>1.2436</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3917</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9585</v>
+        <v>-2.1543</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6585</v>
+        <v>1.1913</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0641</v>
+        <v>0.3876</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7226</v>
+        <v>0.8037</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2754</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4208</v>
+        <v>1.329</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3377</v>
+        <v>1.1924</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.1366</v>
       </c>
       <c r="G5" t="n">
         <v>0.3766</v>
@@ -844,13 +844,13 @@
         <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9908</v>
+        <v>0.899</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9069</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0839</v>
+        <v>0.1373</v>
       </c>
       <c r="V5" t="n">
         <v>-0.73</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3533</v>
+        <v>1.0946</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4107</v>
+        <v>-2.0278</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7639</v>
+        <v>3.1224</v>
       </c>
       <c r="G6" t="n">
         <v>2.9123</v>
@@ -922,13 +922,13 @@
         <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>2.263</v>
+        <v>2.0044</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3305</v>
+        <v>0.7134</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9325</v>
+        <v>1.291</v>
       </c>
       <c r="V6" t="n">
         <v>0.4866</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. REIRIZ MENDEZ</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.119</v>
+        <v>0.1743</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.039</v>
+        <v>-2.3492</v>
       </c>
       <c r="F7" t="n">
-        <v>0.158</v>
+        <v>2.5235</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0473</v>
+        <v>0.7893</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0473</v>
+        <v>0.9358</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.1465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0204</v>
+        <v>-0.873</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0204</v>
+        <v>-0.16</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.713</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0677</v>
+        <v>1.6623</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0677</v>
+        <v>1.0957</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.5666</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1663</v>
+        <v>1.312</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0594</v>
+        <v>0.4823</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2257</v>
+        <v>0.8297</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.9477</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.9477</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>D. REIRIZ MENDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1943</v>
+        <v>0.1144</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2634</v>
+        <v>0.0633</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0691</v>
+        <v>0.0511</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7893</v>
+        <v>-0.0473</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9358</v>
+        <v>-0.0473</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1465</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.873</v>
+        <v>0.0204</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.16</v>
+        <v>0.0204</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.713</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6623</v>
+        <v>-0.0677</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0957</v>
+        <v>-0.0677</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5666</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9434</v>
+        <v>0.1617</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5681</v>
+        <v>0.0429</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3753</v>
+        <v>0.1188</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9477</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2873</v>
+        <v>0.0882</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0924</v>
+        <v>-0.9307</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8051</v>
+        <v>1.0189</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0558</v>
@@ -1156,13 +1156,13 @@
         <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6232</v>
+        <v>-0.2476</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3564</v>
+        <v>-0.1947</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2668</v>
+        <v>-0.0529</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1065</v>
+        <v>-1.083</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0762</v>
+        <v>-2.8121</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9697</v>
+        <v>1.7291</v>
       </c>
       <c r="G10" t="n">
         <v>0.6064000000000001</v>
@@ -1234,13 +1234,13 @@
         <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1672</v>
+        <v>0.1907</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.09</v>
+        <v>0.1741</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2572</v>
+        <v>0.0166</v>
       </c>
       <c r="V10" t="n">
         <v>0.6659</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2152</v>
+        <v>-1.8768</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6565</v>
+        <v>-2.4519</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4414</v>
+        <v>0.575</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0251</v>
@@ -1312,13 +1312,13 @@
         <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0891</v>
+        <v>0.2492</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1782</v>
+        <v>0.0265</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0891</v>
+        <v>0.2228</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1217</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.9833</v>
+        <v>16.8743</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5931</v>
+        <v>-1.702200000000002</v>
       </c>
       <c r="F12" t="n">
-        <v>18.5764</v>
+        <v>18.5765</v>
       </c>
       <c r="G12" t="n">
-        <v>19.0404</v>
+        <v>19.04040000000001</v>
       </c>
       <c r="H12" t="n">
         <v>10.2231</v>
       </c>
       <c r="I12" t="n">
-        <v>8.8172</v>
+        <v>8.817200000000001</v>
       </c>
       <c r="J12" t="n">
         <v>8.291699999999999</v>
@@ -1390,13 +1390,13 @@
         <v>10.7715</v>
       </c>
       <c r="S12" t="n">
-        <v>6.3253</v>
+        <v>7.2165</v>
       </c>
       <c r="T12" t="n">
-        <v>2.808200000000001</v>
+        <v>3.6993</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5171</v>
+        <v>3.5172</v>
       </c>
       <c r="V12" t="n">
         <v>1.3892</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. RAMOS DA CONCEIÇAO</t>
+          <t>H. PALOMARES BARRADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1984</v>
+        <v>0.7573</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7045</v>
+        <v>0.4499</v>
       </c>
       <c r="F13" t="n">
-        <v>2.903</v>
+        <v>0.3074</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5225</v>
+        <v>1.1666</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1042</v>
+        <v>-0.0258</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6266</v>
+        <v>1.1924</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.6047</v>
+        <v>0.6875</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0323</v>
+        <v>0.0408</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.637</v>
+        <v>0.6466</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0822</v>
+        <v>0.4791</v>
       </c>
       <c r="N13" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.0667</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0104</v>
+        <v>0.5458</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.9585</v>
+        <v>0.1958</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7209</v>
+        <v>-0.6052</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8587</v>
+        <v>-0.2376</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8622</v>
+        <v>-0.3676</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. PALOMARES BARRADO</t>
+          <t>S. RAMOS DA CONCEIÇAO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6503</v>
+        <v>-0.2572</v>
       </c>
       <c r="E14" t="n">
-        <v>0.4499</v>
+        <v>-2.6255</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2005</v>
+        <v>2.3683</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1666</v>
+        <v>-0.5225</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.0258</v>
+        <v>0.1042</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1924</v>
+        <v>-0.6266</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6875</v>
+        <v>-0.6047</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0408</v>
+        <v>0.0323</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6466</v>
+        <v>-0.637</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4791</v>
+        <v>0.0822</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0667</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5458</v>
+        <v>0.0104</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1958</v>
+        <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7121</v>
+        <v>0.2652</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2376</v>
+        <v>-0.0623</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4745</v>
+        <v>0.3276</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.4275</v>
+        <v>-0.4578</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8356</v>
+        <v>1.0403</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2632</v>
+        <v>-1.4981</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1727</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.8312</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8269</v>
+        <v>-0.6223</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0261</v>
+        <v>-0.2089</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2166</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-2.3064</v>
+        <v>-1.7837</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.8626</v>
+        <v>-3.0673</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5563</v>
+        <v>1.2836</v>
       </c>
       <c r="G16" t="n">
         <v>-5.4705</v>
@@ -1702,13 +1702,13 @@
         <v>3.7211</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.049</v>
+        <v>-1.5264</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6199</v>
+        <v>-0.8246</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4291</v>
+        <v>-0.7018</v>
       </c>
       <c r="V16" t="n">
         <v>1.492</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. DARRIBA VAZQUEZ</t>
+          <t>D. VILLADONIGA AMADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.3311</v>
+        <v>-1.9731</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6893</v>
+        <v>-0.89</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3582</v>
+        <v>-1.0832</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.8117</v>
+        <v>-1.7957</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.0535</v>
+        <v>-1.3107</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.7582</v>
+        <v>-0.485</v>
       </c>
       <c r="J17" t="n">
-        <v>-4.694</v>
+        <v>-0.3853</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.3295</v>
+        <v>0.2517</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3645</v>
+        <v>-0.637</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1178</v>
+        <v>-1.4104</v>
       </c>
       <c r="N17" t="n">
-        <v>0.276</v>
+        <v>-1.5624</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3938</v>
+        <v>0.152</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5875</v>
+        <v>2.9377</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5875</v>
+        <v>2.9377</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6765</v>
+        <v>-0.6819</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7881</v>
+        <v>-0.5046</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1116</v>
+        <v>-0.1773</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2166</v>
+        <v>-2.4332</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.472</v>
+        <v>-2.3946</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6488</v>
+        <v>-3.0582</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1768</v>
+        <v>0.6635</v>
       </c>
       <c r="G18" t="n">
         <v>-4.2634</v>
@@ -1858,13 +1858,13 @@
         <v>3.917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6602</v>
+        <v>-0.5828</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0623</v>
+        <v>-0.347</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7226</v>
+        <v>-0.2358</v>
       </c>
       <c r="V18" t="n">
         <v>0.4931</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. VILLADONIGA AMADO</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.4792</v>
+        <v>-2.5729</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9923</v>
+        <v>-4.621</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4869</v>
+        <v>2.0482</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7957</v>
+        <v>-1.5382</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3107</v>
+        <v>-0.7951</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.485</v>
+        <v>-0.743</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3853</v>
+        <v>-1.0069</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2517</v>
+        <v>-0.2535</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.637</v>
+        <v>-0.7534</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4104</v>
+        <v>-0.5312</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5624</v>
+        <v>-0.5416</v>
       </c>
       <c r="O19" t="n">
-        <v>0.152</v>
+        <v>0.0104</v>
       </c>
       <c r="P19" t="n">
-        <v>2.9377</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9377</v>
+        <v>2.546</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.188</v>
+        <v>-0.643</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.607</v>
+        <v>-0.6764</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5810999999999999</v>
+        <v>0.0334</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>C. DARRIBA VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2182</v>
+        <v>-2.7644</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.1327</v>
+        <v>-3.0986</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9145</v>
+        <v>0.3342</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5382</v>
+        <v>-4.8117</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7951</v>
+        <v>-3.0535</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.743</v>
+        <v>-1.7582</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0069</v>
+        <v>-4.694</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2535</v>
+        <v>-3.3295</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7534</v>
+        <v>-1.3645</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5312</v>
+        <v>-0.1178</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5416</v>
+        <v>0.276</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0104</v>
+        <v>-0.3938</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.546</v>
+        <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2883</v>
+        <v>0.2432</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.188</v>
+        <v>0.3788</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1003</v>
+        <v>-0.1356</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5977</v>
+        <v>-3.1723</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8317</v>
+        <v>-2.706</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.766</v>
+        <v>-0.4664</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6322</v>
@@ -2092,13 +2092,13 @@
         <v>2.9377</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0242</v>
+        <v>-0.5989</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.7468</v>
+        <v>-0.6211</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2774</v>
+        <v>0.0222</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9412</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-15.9834</v>
+        <v>-14.6187</v>
       </c>
       <c r="E22" t="n">
         <v>-18.5764</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5932</v>
+        <v>3.9575</v>
       </c>
       <c r="G22" t="n">
         <v>-19.0403</v>
@@ -2140,13 +2140,13 @@
         <v>-10.223</v>
       </c>
       <c r="I22" t="n">
-        <v>-8.817200000000001</v>
+        <v>-8.8172</v>
       </c>
       <c r="J22" t="n">
         <v>-10.7485</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.796400000000001</v>
+        <v>-3.7964</v>
       </c>
       <c r="L22" t="n">
         <v>-6.952100000000002</v>
@@ -2170,13 +2170,13 @@
         <v>21.5432</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.3253</v>
+        <v>-4.961</v>
       </c>
       <c r="T22" t="n">
         <v>-3.5171</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8083</v>
+        <v>-1.4438</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3893</v>
